--- a/artfynd/A 37011-2022 artfynd.xlsx
+++ b/artfynd/A 37011-2022 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>115518371</v>
       </c>
       <c r="B2" t="n">
-        <v>56235</v>
+        <v>56347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järkholmen (Järkholmen), Vg</t>
+          <t>Järkholmen, Järkholmen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 37011-2022 artfynd.xlsx
+++ b/artfynd/A 37011-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>115518371</v>
       </c>
       <c r="B2" t="n">
-        <v>56347</v>
+        <v>56441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 37011-2022 artfynd.xlsx
+++ b/artfynd/A 37011-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115518371</v>
       </c>
       <c r="B2" t="n">
-        <v>56441</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,12 +799,7 @@
         <v>115518891</v>
       </c>
       <c r="B3" t="n">
-        <v>56235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,7 +841,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkholmen (Järkholmen), Vg</t>
+          <t>Järkholmen, Järkholmen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -919,6 +909,127 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>115519241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56888</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100041</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Coronella austriaca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Järkholmen, Järkholmen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>316240</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6389163</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Göteborg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Askim</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-08-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-08-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonathan  larsen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jonathan  larsen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37011-2022 artfynd.xlsx
+++ b/artfynd/A 37011-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115518371</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115518891</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,8 +1045,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115519241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>